--- a/backend/data/financials_by_company/1583.HK.xlsx
+++ b/backend/data/financials_by_company/1583.HK.xlsx
@@ -4428,7 +4428,7 @@
         <v>-2241000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>0.483</v>
@@ -4665,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EB2" t="n">
         <v>-0.067200065</v>
